--- a/class documents/schedule.xlsx
+++ b/class documents/schedule.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
-    <t>{Month} {Year} Literatura Digital Calendario de Cursos</t>
+    <t>Mes Year Literatura Digital Calendario de Cursos</t>
   </si>
   <si>
     <t>Área de entrenamiento</t>
@@ -39,11 +39,11 @@
     <t>Facilitador</t>
   </si>
   <si>
-    <t>Literatura Digital {Day1} - {Day2} 
+    <t>Literatura Digital Dia - Dia2 
 11:00AM - 1:00PM</t>
   </si>
   <si>
-    <t>{Date1}</t>
+    <t>Date1</t>
   </si>
   <si>
     <t>Teclado/escritura/ratón</t>
@@ -56,7 +56,7 @@
     <t>Jesus Arambula</t>
   </si>
   <si>
-    <t>{Date2}</t>
+    <t>Date2</t>
   </si>
   <si>
     <t>Correo electrónico/Gmail</t>
@@ -65,7 +65,7 @@
     <t>Cómo utilizar Correo electrónico + Gmail</t>
   </si>
   <si>
-    <t>{Date3}</t>
+    <t>Date3</t>
   </si>
   <si>
     <t>Realizar búsquedas en Internet</t>
@@ -74,7 +74,7 @@
     <t>Aprenda a utilizar un navegador y un motor de búsqueda para búsquedas en Internet</t>
   </si>
   <si>
-    <t>{Date4}</t>
+    <t>Date4</t>
   </si>
   <si>
     <t>Conciencia de seguridad</t>
@@ -83,7 +83,7 @@
     <t>Aprenda a utilizar y navegar por Internet de forma segura + protocolos de seguridad</t>
   </si>
   <si>
-    <t>{Date5}</t>
+    <t>Date5</t>
   </si>
   <si>
     <t>Videoconferencia</t>
@@ -92,7 +92,7 @@
     <t>Cómo utilizar Zoom</t>
   </si>
   <si>
-    <t>{Date6}</t>
+    <t>Date6</t>
   </si>
   <si>
     <t>Google Docs</t>
@@ -101,7 +101,7 @@
     <t>Cómo utilizar Google Drive y Documentos de Google</t>
   </si>
   <si>
-    <t>{Date7}</t>
+    <t>Date7</t>
   </si>
   <si>
     <t>Google Sheets</t>
@@ -110,7 +110,7 @@
     <t>Cómo utilizar Hojas de cálculo de Google</t>
   </si>
   <si>
-    <t>{Date8}</t>
+    <t>Date8</t>
   </si>
   <si>
     <t>Solución de problemas básicos</t>
